--- a/out/MLP-mamba2_repeat_1_000006.xlsx
+++ b/out/MLP-mamba2_repeat_1_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.443559541701984</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8815939771807735</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8815939771807735</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.443559541701984</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.443559541701984</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8815939771807735</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.443559541701984</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.8241370729394373</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8815939771807735</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.443559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.424137072939437</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.443559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8815939771807735</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.043559541701984</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.8241370729394373</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003345784622927895</v>
+        <v>-0.0003248462797255488</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4306283329165056</v>
+        <v>0.4181024663142252</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8815939771807735</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8620720436675998</v>
+        <v>0.8369961836136819</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.09944987949468483</v>
+        <v>-0.09655704483390672</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.330843874959528</v>
+        <v>0.3212205752005929</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.443559541701984</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.330843874959528</v>
+        <v>0.3212205752005929</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.043559541701984</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3304815969553413</v>
+        <v>0.3209371627374988</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.112996216210163</v>
+        <v>0.8707043800460124</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.558690590164945</v>
+        <v>2.064079698758126</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2129592851159403</v>
+        <v>0.1665994723264214</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.443559541701984</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.869988543380497</v>
+        <v>1.525303640722092</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.3730183845323038</v>
+        <v>0.2918145582187243</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.443559541701984</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.403170729679898</v>
+        <v>1.942415386092743</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.2042786799930948</v>
+        <v>0.1598085096481665</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8815939771807735</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.438387750376402</v>
+        <v>1.969965885204775</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.08436987299492761</v>
+        <v>0.06600304501060202</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.402635062636414</v>
+        <v>1.94199633044184</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1051176216169958</v>
+        <v>0.08223462050359277</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.52851518208054</v>
+        <v>2.040473211197394</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.06329497709783764</v>
+        <v>0.04951527339120954</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.549915200422109</v>
+        <v>2.057214515282083</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.04812119807243218</v>
+        <v>0.03764491888172949</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.582835572751116</v>
+        <v>2.08296853694719</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0212833367475067</v>
+        <v>0.01665044558927069</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.577240196226289</v>
+        <v>2.078591099560023</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01688848798261751</v>
+        <v>0.01321138990144965</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.443559541701984</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.589727104383578</v>
+        <v>2.088359235288057</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.008372457401808602</v>
+        <v>0.006548878289859224</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.443559541701984</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.589572566804399</v>
+        <v>2.08823724407011</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.004867911248929481</v>
+        <v>0.003806052976774699</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.043559541701984</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.59092900432228</v>
+        <v>2.089297418339204</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002430001024091926</v>
+        <v>0.001900526488387349</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8815939771807735</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.59092097258163</v>
+        <v>2.089290045830093</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001199477580037933</v>
+        <v>0.0009378845972611983</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.590885482441555</v>
+        <v>2.089261177653615</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.000692569430581672</v>
+        <v>0.0005423750555760488</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.424137072939437</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.591073849839377</v>
+        <v>2.089407547171592</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002293568619670503</v>
+        <v>0.0001780215493456964</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.590836082620852</v>
+        <v>2.089220767058077</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001117811396580942</v>
+        <v>8.707743703811276e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.590832388667517</v>
+        <v>2.089216785915194</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>5.860109938282116e-05</v>
+        <v>4.392392260217012e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.590837943179844</v>
+        <v>2.089219951073697</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.58123458105224e-05</v>
+        <v>1.870180446963262e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.443559541701984</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.590830849621383</v>
+        <v>2.089213323080956</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.536440521940679e-05</v>
+        <v>9.546003728147707e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8241370729394373</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.590833379616926</v>
+        <v>2.089214241317101</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8815939771807735</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.590826045222782</v>
+        <v>2.08920723902628</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.590822560002474</v>
+        <v>2.089203376951184</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.590818012690289</v>
+        <v>2.089198829638999</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.590818102634939</v>
+        <v>2.089198919583649</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.590817244701354</v>
+        <v>2.089198061650064</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.590817473022389</v>
+        <v>2.089198289971099</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.590816677358177</v>
+        <v>2.089197494306887</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.59081673962755</v>
+        <v>2.08919755657626</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.590816767302827</v>
+        <v>2.089197584251537</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.59081691951685</v>
+        <v>2.08919773646556</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8815939771807735</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.590816573575888</v>
+        <v>2.089197390524598</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8815939771807735</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.5908166496829</v>
+        <v>2.08919746663161</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.590816815734561</v>
+        <v>2.089197632683272</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.590817175513161</v>
+        <v>2.089197992461871</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.590817196269619</v>
+        <v>2.089198013218329</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.590817300051908</v>
+        <v>2.089198117000618</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8815939771807735</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.590817528372943</v>
+        <v>2.089198345321652</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.590817403834196</v>
+        <v>2.089198220782906</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.590817431509473</v>
+        <v>2.089198248458183</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.443559541701984</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.590817486860027</v>
+        <v>2.089198303808737</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.590817749775158</v>
+        <v>2.089198566723868</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.590817666749327</v>
+        <v>2.089198483698037</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.59081745918475</v>
+        <v>2.08919827613346</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.590817473022389</v>
+        <v>2.089198289971099</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.590817611398773</v>
+        <v>2.089198428347483</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.590817327727184</v>
+        <v>2.089198144675894</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.590817154756704</v>
+        <v>2.089197971705414</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.590817050974416</v>
+        <v>2.089197867923126</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.590817196269619</v>
+        <v>2.089198013218329</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8815939771807735</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.590817438428293</v>
+        <v>2.089198255377002</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8815939771807735</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.590817265457812</v>
+        <v>2.089198082406522</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.590816967948585</v>
+        <v>2.089197784897295</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.590816954110946</v>
+        <v>2.089197771059656</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.590816587413526</v>
+        <v>2.089197404362237</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.590816587413526</v>
+        <v>2.089197404362237</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8815939771807735</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.590816525144154</v>
+        <v>2.089197342092864</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8815939771807735</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.590816421361865</v>
+        <v>2.089197238310575</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.590816248391384</v>
+        <v>2.089197065340094</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.590816296823119</v>
+        <v>2.089197113771829</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.590815937044519</v>
+        <v>2.089196753993229</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.590815895531604</v>
+        <v>2.089196712480314</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.590815950882157</v>
+        <v>2.089196767830867</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8815939771807735</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.590816006232711</v>
+        <v>2.089196823181422</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8815939771807735</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.590816047745627</v>
+        <v>2.089196864694337</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.590815777911676</v>
+        <v>2.089196594860387</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.59081583326223</v>
+        <v>2.08919665021094</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8815939771807735</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.590815978557434</v>
+        <v>2.089196795506144</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.590815943963338</v>
+        <v>2.089196760912048</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.5908159301257</v>
+        <v>2.08919674707441</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.59081602007035</v>
+        <v>2.08919683701906</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.043559541701984</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.590816338336034</v>
+        <v>2.089197155284744</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8815939771807735</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.590816158446734</v>
+        <v>2.089196975395444</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.59081619995965</v>
+        <v>2.08919701690836</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.424137072939437</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.590816013151531</v>
+        <v>2.089196830100241</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.590816082339723</v>
+        <v>2.089196899288433</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.590815881693965</v>
+        <v>2.089196698642675</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.424137072939437</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.590815923206881</v>
+        <v>2.089196740155591</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.043559541701984</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.590815950882157</v>
+        <v>2.089196767830867</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_1_000006.xlsx
+++ b/out/MLP-mamba2_repeat_1_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.443559541701984</v>
+        <v>0.5001101738204643</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.043559541701984</v>
+        <v>0.04463666190242505</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.044636661902425</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.155363338097575</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.155363338097575</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.443559541701984</v>
+        <v>0.5001101738204644</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.04463666190242516</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.04463666190242516</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.04463666190242516</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975748</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.1553633380975748</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975748</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.04463666190242516</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.043559541701984</v>
+        <v>0.04463666190242523</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.04463666190242523</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.04463666190242523</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204646</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003345784622927895</v>
+        <v>-0.0001803651396274799</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4306283329165056</v>
+        <v>0.2321439844688374</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.04463666190242523</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8620720436675998</v>
+        <v>0.4647272970240307</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.09944987949468483</v>
+        <v>-0.05361158788150551</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975748</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.330843874959528</v>
+        <v>0.1783520314477044</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.443559541701984</v>
+        <v>0.5001101738204644</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.330843874959528</v>
+        <v>0.1783520314477044</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.043559541701984</v>
+        <v>0.5001101738204645</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3304815969553413</v>
+        <v>0.1781845337399493</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.112996216210163</v>
+        <v>0.5145891828395064</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.558690590164945</v>
+        <v>1.208387566755859</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2129592851159403</v>
+        <v>0.09846084192365695</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.443559541701984</v>
+        <v>0.5001101738204644</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.869988543380497</v>
+        <v>0.8899691255581686</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.3730183845323038</v>
+        <v>0.1724635024674204</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.443559541701984</v>
+        <v>0.5001101738204644</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.403170729679898</v>
+        <v>1.136483553316881</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.2042786799930948</v>
+        <v>0.0944470517387625</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.438387750376402</v>
+        <v>1.152765978169654</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.08436987299492761</v>
+        <v>0.03900800782766479</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.402635062636414</v>
+        <v>1.136235849109109</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1051176216169958</v>
+        <v>0.04860063031157812</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.52851518208054</v>
+        <v>1.194436237323696</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.06329497709783764</v>
+        <v>0.02926385730599275</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.549915200422109</v>
+        <v>1.204330541922209</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.04812119807243218</v>
+        <v>0.02224929652227409</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.582835572751116</v>
+        <v>1.219551591166852</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0212833367475067</v>
+        <v>0.009839075054091732</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.577240196226289</v>
+        <v>1.21696266798611</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01688848798261751</v>
+        <v>0.007806289985646866</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.443559541701984</v>
+        <v>0.5001101738204644</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.589727104383578</v>
+        <v>1.222733337571224</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.008372457401808602</v>
+        <v>0.003867291447596213</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.443559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.589572566804399</v>
+        <v>1.222659206023016</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.004867911248929481</v>
+        <v>0.002246721377117265</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.59092900432228</v>
+        <v>1.223283720286389</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002430001024091926</v>
+        <v>0.001120860688558633</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.59092097258163</v>
+        <v>1.223277318513831</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001199477580037933</v>
+        <v>0.0005526817435020503</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.590885482441555</v>
+        <v>1.22325820136067</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.000692569430581672</v>
+        <v>0.0003187523194565654</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.591073849839377</v>
+        <v>1.223342730892643</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002293568619670503</v>
+        <v>0.0001021345654706516</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.590836082620852</v>
+        <v>1.22323021601024</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001117811396580942</v>
+        <v>4.889898753450504e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.590832388667517</v>
+        <v>1.223225826252045</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>5.860109938282116e-05</v>
+        <v>2.435435356130208e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.590837943179844</v>
+        <v>1.22322580560545</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.58123458105224e-05</v>
+        <v>9.221082681779568e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.590830849621383</v>
+        <v>1.223219798367001</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.536440521940679e-05</v>
+        <v>3.727602236888622e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.590833379616926</v>
+        <v>1.223218565175848</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.732487839350877e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.590826045222782</v>
+        <v>1.223212230315301</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.590822560002474</v>
+        <v>1.223207987705147</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.04463666190242516</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.590818012690289</v>
+        <v>1.223208216026182</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.6108368500156143</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.590818102634939</v>
+        <v>1.223208305970832</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.590817244701354</v>
+        <v>1.223207448037247</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.590817473022389</v>
+        <v>1.223207676358282</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.590816677358177</v>
+        <v>1.22320688069407</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.59081673962755</v>
+        <v>1.223206942963443</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975748</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.590816767302827</v>
+        <v>1.22320697063872</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.1553633380975748</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.59081691951685</v>
+        <v>1.223207122852743</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.590816573575888</v>
+        <v>1.223206776911781</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.043559541701984</v>
+        <v>0.04463666190242521</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.5908166496829</v>
+        <v>1.223206853018793</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.590816815734561</v>
+        <v>1.223207019070454</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.590817175513161</v>
+        <v>1.223207378849054</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.590817196269619</v>
+        <v>1.223207399605512</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.590817300051908</v>
+        <v>1.2232075033878</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.04463666190242516</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.590817528372943</v>
+        <v>1.223207731708835</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.590817403834196</v>
+        <v>1.223207607170089</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975748</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.590817431509473</v>
+        <v>1.223207634845366</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.1553633380975748</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.590817486860027</v>
+        <v>1.22320769019592</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975748</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.590817749775158</v>
+        <v>1.223207953111051</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.590817666749327</v>
+        <v>1.22320787008522</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.59081745918475</v>
+        <v>1.223207662520643</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.590817473022389</v>
+        <v>1.223207676358282</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.590817611398773</v>
+        <v>1.223207814734666</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.590817327727184</v>
+        <v>1.223207531063077</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975748</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.590817154756704</v>
+        <v>1.223207358092597</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.590817050974416</v>
+        <v>1.223207254310309</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.590817196269619</v>
+        <v>1.223207399605512</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.04463666190242516</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.590817438428293</v>
+        <v>1.223207641764185</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.6108368500156143</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.590817265457812</v>
+        <v>1.223207468793705</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.590816967948585</v>
+        <v>1.223207171284478</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.590816954110946</v>
+        <v>1.223207157446839</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975748</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.590816587413526</v>
+        <v>1.22320679074942</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.1553633380975748</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.590816587413526</v>
+        <v>1.22320679074942</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.04463666190242521</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.590816525144154</v>
+        <v>1.223206728480047</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.590816421361865</v>
+        <v>1.223206624697758</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.590816248391384</v>
+        <v>1.223206451727277</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.590816296823119</v>
+        <v>1.223206500159012</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975748</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.590815937044519</v>
+        <v>1.223206140380412</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.590815895531604</v>
+        <v>1.223206098867496</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.590815950882157</v>
+        <v>1.22320615421805</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.04463666190242516</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.590816006232711</v>
+        <v>1.223206209568604</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.6108368500156143</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.590816047745627</v>
+        <v>1.22320625108152</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975748</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.590815777911676</v>
+        <v>1.22320598124757</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.1553633380975748</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.59081583326223</v>
+        <v>1.223206036598123</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.590815978557434</v>
+        <v>1.223206181893327</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.043559541701984</v>
+        <v>0.04463666190242521</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.590815943963338</v>
+        <v>1.223206147299231</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.5908159301257</v>
+        <v>1.223206133461593</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.59081602007035</v>
+        <v>1.223206223406243</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.590816338336034</v>
+        <v>1.223206541671927</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.04463666190242516</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.590816158446734</v>
+        <v>1.223206361782627</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.59081619995965</v>
+        <v>1.223206403295543</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.590816013151531</v>
+        <v>1.223206216487424</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.590816082339723</v>
+        <v>1.223206285675616</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.590815881693965</v>
+        <v>1.223206085029858</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.590815923206881</v>
+        <v>1.223206126542774</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.043559541701984</v>
+        <v>0.1723734178614448</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.590815950882157</v>
+        <v>1.22320615421805</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_1_000006.xlsx
+++ b/out/MLP-mamba2_repeat_1_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.3820018470287323</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.1600000000000003</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4721771776676178</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.1600000000000002</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.5017948746681213</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.5001101738204643</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.7001180052757263</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.1959680467844009</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.6651585698127747</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.04463666190242505</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.2942158281803131</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.5742742419242859</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.5581557750701904</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.7001101738204644</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.2146500051021576</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.044636661902425</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4445747435092926</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.362021267414093</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.6830347776412964</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.155363338097575</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.2935579121112823</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.155363338097575</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.2999268472194672</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.2863980829715729</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.5394715070724487</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.5001101738204644</v>
+        <v>0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.5754284858703613</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.355583685738504</v>
+        <v>0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.7061500549316406</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.3767211437225342</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.04463666190242516</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.2301390469074249</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.3590511381626129</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3331065475940704</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.7435551285743713</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.2511000633239746</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.9185657501220703</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.6495149731636047</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.4773359298706055</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.04463666190242516</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.3431507349014282</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.04463666190242516</v>
+        <v>0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.6056117415428162</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.1553633380975749</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.3152565658092499</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.2792152762413025</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4901300966739655</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.1553633380975748</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.7629596590995789</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.1553633380975748</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.3953564465045929</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.1553633380975748</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4338483214378357</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.04463666190242516</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.6777981519699097</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.04463666190242523</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.332987904548645</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.04463666190242523</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.4842433631420135</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.04463666190242523</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.513627827167511</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.8234682679176331</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.355583685738504</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.9177984595298767</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.355583685738504</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.9197144508361816</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.7001101738204646</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001803651396274799</v>
+        <v>-0.0001505071560592624</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2321439844688374</v>
+        <v>0.1937144337915407</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>0.4118847548961639</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.04463666190242523</v>
+        <v>0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4647272970240307</v>
+        <v>0.3877954684738684</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.05361158788150551</v>
+        <v>-0.04473662505144678</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.03611407428979874</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.1553633380975748</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1783520314477044</v>
+        <v>0.1488273015840347</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.7694879174232483</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.5001101738204644</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1783520314477044</v>
+        <v>0.1488273015840347</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.8001024127006531</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.5001101738204645</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1781845337399493</v>
+        <v>0.1487550174629798</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.5145891828395064</v>
+        <v>0.2220724527183046</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.2435752749443054</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.7001101738204645</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.208387566755859</v>
+        <v>0.5933421210574857</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.09846084192365695</v>
+        <v>0.04249106159216588</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.898772120475769</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.5001101738204644</v>
+        <v>-0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8899691255581686</v>
+        <v>0.4559277202391059</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.1724635024674204</v>
+        <v>0.07442712414977931</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.6296346783638</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.5001101738204644</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.136483553316881</v>
+        <v>0.5623117357381268</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0944470517387625</v>
+        <v>0.04075900163180279</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.459296703338623</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.152765978169654</v>
+        <v>0.5693384631679523</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.03900800782766479</v>
+        <v>0.01683406125898829</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.8440675139427185</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.136235849109109</v>
+        <v>0.5622048559150095</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.04860063031157812</v>
+        <v>0.0209733053068108</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.9542284607887268</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.355583685738504</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.194436237323696</v>
+        <v>0.5873212124477022</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.02926385730599275</v>
+        <v>0.01262836336797664</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.7698124647140503</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.355583685738504</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.204330541922209</v>
+        <v>0.5915902860940718</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.02224929652227409</v>
+        <v>0.009599664042752726</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.8901600241661072</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.219551591166852</v>
+        <v>0.5981569335121708</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.009839075054091732</v>
+        <v>0.00424317769124753</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.4605090022087097</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.21696266798611</v>
+        <v>0.5970368500988474</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.007806289985646866</v>
+        <v>0.003364674982507011</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.7135618925094604</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.5001101738204644</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.222733337571224</v>
+        <v>0.5995243225849434</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.003867291447596213</v>
+        <v>0.001665988815887771</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.9878941178321838</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.355583685738504</v>
+        <v>-0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.222659206023016</v>
+        <v>0.5994894788253274</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002246721377117265</v>
+        <v>0.0009666730490402668</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.7737290859222412</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.7001101738204645</v>
+        <v>-0.3</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.223283720286389</v>
+        <v>0.59975636174072</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001120860688558633</v>
+        <v>0.0004808365245201334</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.06044160947203636</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.223277318513831</v>
+        <v>0.5997507568414505</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0005526817435020503</v>
+        <v>0.000236470445640063</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.354610800743103</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.22325820136067</v>
+        <v>0.5997396442596696</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0003187523194565654</v>
+        <v>0.0001351814166719149</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.1497020125389099</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.223342730892643</v>
+        <v>0.5997734096240291</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001021345654706516</v>
+        <v>4.187137239341006e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.06449666619300842</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.22323021601024</v>
+        <v>0.5997218561803243</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>4.889898753450504e-05</v>
+        <v>1.745791147271043e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>0.3323158323764801</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.223225826252045</v>
+        <v>0.5997171185196988</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.435435356130208e-05</v>
+        <v>7.230980650542531e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.1528001725673676</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.22322580560545</v>
+        <v>0.5997143102936427</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>9.221082681779568e-06</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.8411154747009277</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.223219798367001</v>
+        <v>0.5997088447279239</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>3.727602236888622e-06</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.3858078122138977</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.223218565175848</v>
+        <v>0.599705460109473</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.5977635383605957</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.223212230315301</v>
+        <v>0.5996997926791993</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.7479641437530518</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.223207987705147</v>
+        <v>0.5997001732142569</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.108778789639473</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.04463666190242516</v>
+        <v>0.16</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.223208216026182</v>
+        <v>0.5997004015352917</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.06040193513035774</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6108368500156143</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.223208305970832</v>
+        <v>0.5997004914799416</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.2268065959215164</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.223207448037247</v>
+        <v>0.5996996335463568</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.0971396416425705</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.223207676358282</v>
+        <v>0.5996998618673915</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.3263620138168335</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.22320688069407</v>
+        <v>0.5996990662031798</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.1908124834299088</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.223206942963443</v>
+        <v>0.5996991284725529</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.4806723892688751</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.1553633380975748</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.22320697063872</v>
+        <v>0.5996991561478298</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.5438910722732544</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.1553633380975748</v>
+        <v>0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.223207122852743</v>
+        <v>0.599699308361853</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.2066087126731873</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.3</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.223206776911781</v>
+        <v>0.5996989624208913</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.6463901996612549</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.04463666190242521</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.223206853018793</v>
+        <v>0.599699038527903</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.2421368956565857</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.223207019070454</v>
+        <v>0.5996992045795645</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.9047724604606628</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.223207378849054</v>
+        <v>0.5996995643581645</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.6160274147987366</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.355583685738504</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.223207399605512</v>
+        <v>0.5996995851146223</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.7943682074546814</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.2232075033878</v>
+        <v>0.5996996888969107</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.2332628965377808</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.04463666190242516</v>
+        <v>0.16</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.223207731708835</v>
+        <v>0.5996999172179455</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.2740322351455688</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.223207607170089</v>
+        <v>0.5996997926791993</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3682883977890015</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.1553633380975748</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.223207634845366</v>
+        <v>0.5996998203544761</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.8212683796882629</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.1553633380975748</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.22320769019592</v>
+        <v>0.59969987570503</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.1304488480091095</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.1553633380975748</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.223207953111051</v>
+        <v>0.5997001386201608</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.4043383002281189</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.22320787008522</v>
+        <v>0.5997000555943299</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.4231703877449036</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.223207662520643</v>
+        <v>0.5996998480297532</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4857547879219055</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.223207676358282</v>
+        <v>0.5996998618673915</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.2766219675540924</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.16</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.223207814734666</v>
+        <v>0.5997000002437762</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.1785897463560104</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.223207531063077</v>
+        <v>0.5996997165721876</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.2556009590625763</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1553633380975748</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.223207358092597</v>
+        <v>0.5996995436017069</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.7519227266311646</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7001101738204645</v>
+        <v>-0.16</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.223207254310309</v>
+        <v>0.5996994398194183</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.609093189239502</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7001101738204645</v>
+        <v>-0.16</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.223207399605512</v>
+        <v>0.5996995851146223</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.4370555281639099</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.04463666190242516</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.223207641764185</v>
+        <v>0.5996998272732955</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.09888438135385513</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6108368500156143</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.223207468793705</v>
+        <v>0.5996996543028145</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.3534956872463226</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.223207171284478</v>
+        <v>0.5996993567935875</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.08916309475898743</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.223207157446839</v>
+        <v>0.5996993429559491</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3624163568019867</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1553633380975748</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.22320679074942</v>
+        <v>0.5996989762585299</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.720008909702301</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.1553633380975748</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.22320679074942</v>
+        <v>0.5996989762585299</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.1596280783414841</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.04463666190242521</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.223206728480047</v>
+        <v>0.5996989139891568</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.2140064388513565</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.223206624697758</v>
+        <v>0.5996988102068682</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.3775958120822906</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.223206451727277</v>
+        <v>0.5996986372363875</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.1266270726919174</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.223206500159012</v>
+        <v>0.599698685668122</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.1726993918418884</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.1553633380975748</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.223206140380412</v>
+        <v>0.599698325889522</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.5061798095703125</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.223206098867496</v>
+        <v>0.5996982843766065</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.5600147843360901</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.22320615421805</v>
+        <v>0.5996983397271602</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.2871940433979034</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.04463666190242516</v>
+        <v>0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.223206209568604</v>
+        <v>0.5996983950777143</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.2120812684297562</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6108368500156143</v>
+        <v>0.16</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.22320625108152</v>
+        <v>0.5996984365906296</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.2383741587400436</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.1553633380975748</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.22320598124757</v>
+        <v>0.5996981667566795</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.6437574625015259</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.1553633380975748</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.223206036598123</v>
+        <v>0.5996982221072334</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.2904787659645081</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.16</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.223206181893327</v>
+        <v>0.5996983674024374</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.502220094203949</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.04463666190242521</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.223206147299231</v>
+        <v>0.5996983328083412</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.2680416703224182</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.223206133461593</v>
+        <v>0.5996983189707026</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.9296727180480957</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.223206223406243</v>
+        <v>0.5996984089153528</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.8726257681846619</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.223206541671927</v>
+        <v>0.5996987271810374</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.08373048901557922</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.04463666190242516</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.223206361782627</v>
+        <v>0.5996985472917373</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.219901978969574</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.16</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.223206403295543</v>
+        <v>0.5996985888046527</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4606596231460571</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.223206216487424</v>
+        <v>0.5996984019965333</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.1430396139621735</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.223206285675616</v>
+        <v>0.5996984711847259</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3756689429283142</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.223206085029858</v>
+        <v>0.5996982705389681</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.4197295308113098</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.1553633380975749</v>
+        <v>0.72</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.223206126542774</v>
+        <v>0.5996983120518834</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.6319540143013</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.1723734178614448</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.22320615421805</v>
+        <v>0.5996983397271602</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_1_000006.xlsx
+++ b/out/MLP-mamba2_repeat_1_000006.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.3820018470287323</v>
+        <v>0.3820013999938965</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.1600000000000003</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.4721771776676178</v>
+        <v>0.4721767902374268</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.1600000000000002</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.5017948746681213</v>
+        <v>0.5017945170402527</v>
       </c>
       <c r="JB4" t="n">
         <v>0.4399999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.1959680467844009</v>
+        <v>0.1959678083658218</v>
       </c>
       <c r="JB6" t="n">
         <v>0.4399999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.6651585698127747</v>
+        <v>0.6651582717895508</v>
       </c>
       <c r="JB7" t="n">
         <v>0.4399999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.2942158281803131</v>
+        <v>0.2942155003547668</v>
       </c>
       <c r="JB8" t="n">
         <v>0.3</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.2146500051021576</v>
+        <v>0.2146497219800949</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.5799999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.4445747435092926</v>
+        <v>0.4445744156837463</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.5799999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.362021267414093</v>
+        <v>0.3620209097862244</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.7199999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.6830347776412964</v>
+        <v>0.6830344796180725</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.7199999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.2935579121112823</v>
+        <v>0.2935576736927032</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.7199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.2999268472194672</v>
+        <v>0.2999265193939209</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.4399999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.2863980829715729</v>
+        <v>0.2863978445529938</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.5799999999999998</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.5394715070724487</v>
+        <v>0.5394711494445801</v>
       </c>
       <c r="JB18" t="n">
         <v>0.3</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.5754284858703613</v>
+        <v>0.5754281878471375</v>
       </c>
       <c r="JB19" t="n">
         <v>0.3</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.7061500549316406</v>
+        <v>0.7061501741409302</v>
       </c>
       <c r="JB20" t="n">
         <v>0.3</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.3767211437225342</v>
+        <v>0.3767208158969879</v>
       </c>
       <c r="JB21" t="n">
         <v>0.02000000000000007</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.2301390469074249</v>
+        <v>0.230138823390007</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.1199999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.3590511381626129</v>
+        <v>0.359050840139389</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.7199999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.3331065475940704</v>
+        <v>0.3331062495708466</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.7199999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.7435551285743713</v>
+        <v>0.7435552477836609</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.4399999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.2511000633239746</v>
+        <v>0.2510998249053955</v>
       </c>
       <c r="JB26" t="n">
         <v>0.4399999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.4773359298706055</v>
+        <v>0.4773359894752502</v>
       </c>
       <c r="JB29" t="n">
         <v>0.5799999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.3152565658092499</v>
+        <v>0.3152563273906708</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.4399999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.2792152762413025</v>
+        <v>0.2792150378227234</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.1600000000000001</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.4901300966739655</v>
+        <v>0.4901298582553864</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.4399999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.4338483214378357</v>
+        <v>0.4338483512401581</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.4399999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.6777981519699097</v>
+        <v>0.6777982115745544</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.5799999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.332987904548645</v>
+        <v>0.3329877257347107</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.3</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.4118847548961639</v>
+        <v>0.4118847250938416</v>
       </c>
       <c r="JB45" t="n">
         <v>0.3</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.459296703338623</v>
+        <v>0.4592966735363007</v>
       </c>
       <c r="JB52" t="n">
         <v>0.7199999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.8440675139427185</v>
+        <v>0.8440674543380737</v>
       </c>
       <c r="JB53" t="n">
         <v>0.5799999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.4605090022087097</v>
+        <v>0.4605090916156769</v>
       </c>
       <c r="JB57" t="n">
         <v>0.4399999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.7135618925094604</v>
+        <v>0.713562548160553</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.02000000000000007</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.354610800743103</v>
+        <v>0.3546108901500702</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.7199999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.1497020125389099</v>
+        <v>0.1497021168470383</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.06449666619300842</v>
+        <v>0.06449665129184723</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.3323158323764801</v>
+        <v>0.3323157727718353</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.7199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.1528001725673676</v>
+        <v>0.1528003960847855</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.7199999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.8411154747009277</v>
+        <v>0.8411155939102173</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.4399999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.3858078122138977</v>
+        <v>0.3858077824115753</v>
       </c>
       <c r="JB68" t="n">
         <v>0.4399999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.7479641437530518</v>
+        <v>0.747964084148407</v>
       </c>
       <c r="JB70" t="n">
         <v>0.1600000000000001</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.108778789639473</v>
+        <v>0.1087787449359894</v>
       </c>
       <c r="JB71" t="n">
         <v>0.16</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.2268065959215164</v>
+        <v>0.2268066257238388</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.3263620138168335</v>
+        <v>0.3263619542121887</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.8599999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.5438910722732544</v>
+        <v>0.5438910126686096</v>
       </c>
       <c r="JB78" t="n">
         <v>0.3</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.6160274147987366</v>
+        <v>0.6160273551940918</v>
       </c>
       <c r="JB83" t="n">
         <v>0.4399999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.7943682074546814</v>
+        <v>0.7943683266639709</v>
       </c>
       <c r="JB84" t="n">
         <v>0.4399999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.2332628965377808</v>
+        <v>0.2332628071308136</v>
       </c>
       <c r="JB85" t="n">
         <v>0.16</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.3682883977890015</v>
+        <v>0.3682883381843567</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.7199999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.8212683796882629</v>
+        <v>0.8212684988975525</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.4399999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.4043383002281189</v>
+        <v>0.4043383896350861</v>
       </c>
       <c r="JB90" t="n">
         <v>0.7199999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.4231703877449036</v>
+        <v>0.4231702983379364</v>
       </c>
       <c r="JB91" t="n">
         <v>0.4399999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.1785897463560104</v>
+        <v>0.178589716553688</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.4399999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.2556009590625763</v>
+        <v>0.2556016147136688</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.4399999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.7519227266311646</v>
+        <v>0.751922607421875</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.16</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.4370555281639099</v>
+        <v>0.4370563924312592</v>
       </c>
       <c r="JB98" t="n">
         <v>0.4399999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.09888438135385513</v>
+        <v>0.09888465702533722</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.4399999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.3534956872463226</v>
+        <v>0.3534963428974152</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.08916309475898743</v>
+        <v>0.08916305005550385</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.7199999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.3624163568019867</v>
+        <v>0.3624170124530792</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.7199999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.720008909702301</v>
+        <v>0.7200087904930115</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.7199999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.2140064388513565</v>
+        <v>0.2140069752931595</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.7199999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.3775958120822906</v>
+        <v>0.3775964081287384</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.1266270726919174</v>
+        <v>0.126627042889595</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.7199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.1726993918418884</v>
+        <v>0.1726997345685959</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.4399999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.5061798095703125</v>
+        <v>0.5061803460121155</v>
       </c>
       <c r="JB109" t="n">
         <v>0.1600000000000001</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.5600147843360901</v>
+        <v>0.5600147247314453</v>
       </c>
       <c r="JB110" t="n">
         <v>0.1600000000000001</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.2871940433979034</v>
+        <v>0.287194550037384</v>
       </c>
       <c r="JB111" t="n">
         <v>0.16</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.2120812684297562</v>
+        <v>0.2120816558599472</v>
       </c>
       <c r="JB112" t="n">
         <v>0.16</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.2383741587400436</v>
+        <v>0.2383745759725571</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.1199999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.6437574625015259</v>
+        <v>0.6437579393386841</v>
       </c>
       <c r="JB114" t="n">
         <v>0.1600000000000001</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.2904787659645081</v>
+        <v>0.290479302406311</v>
       </c>
       <c r="JB115" t="n">
         <v>0.16</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.502220094203949</v>
+        <v>0.502220630645752</v>
       </c>
       <c r="JB116" t="n">
         <v>0.4399999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.2680416703224182</v>
+        <v>0.2680420875549316</v>
       </c>
       <c r="JB117" t="n">
         <v>0.4399999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.08373048901557922</v>
+        <v>0.08373046666383743</v>
       </c>
       <c r="JB120" t="n">
         <v>0.4399999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.219901978969574</v>
+        <v>0.2199019640684128</v>
       </c>
       <c r="JB121" t="n">
         <v>0.16</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.1430396139621735</v>
+        <v>0.1430399417877197</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.3756689429283142</v>
+        <v>0.3756688833236694</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.02000000000000007</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.4197295308113098</v>
+        <v>0.41973015666008</v>
       </c>
       <c r="JB125" t="n">
         <v>0.72</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.6319540143013</v>
+        <v>0.6319538950920105</v>
       </c>
       <c r="JB126" t="n">
         <v>0.8599999999999999</v>
